--- a/demo/data/остатки-фулфилмент.xlsx
+++ b/demo/data/остатки-фулфилмент.xlsx
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -540,7 +540,7 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -554,7 +554,7 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -568,7 +568,7 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -582,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -596,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -610,7 +610,7 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -624,7 +624,7 @@
         <v>17</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -638,7 +638,7 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -904,7 +904,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -918,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="D33">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -946,7 +946,7 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -960,7 +960,7 @@
         <v>11</v>
       </c>
       <c r="D36">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -974,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="D37">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -988,7 +988,7 @@
         <v>13</v>
       </c>
       <c r="D38">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1002,7 +1002,7 @@
         <v>14</v>
       </c>
       <c r="D39">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1016,7 +1016,7 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1030,7 +1030,7 @@
         <v>16</v>
       </c>
       <c r="D41">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1044,7 +1044,7 @@
         <v>17</v>
       </c>
       <c r="D42">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1058,7 +1058,7 @@
         <v>18</v>
       </c>
       <c r="D43">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:4">
